--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -8,18 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +208,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>iFAST Global Bank Limited — Cash Flow Summary by Year</a:t>
+              <a:t>iFAST Global Bank Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -401,6 +406,528 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>iFAST Global Bank Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$16:$V$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>iFAST Global Bank Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>iFAST Global Bank Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$23:$AL$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$23:$AL$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$23:$AL$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$23:$AL$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>iFAST Global Bank Limited — Pillar 3 Key Metrics by Year</a:t>
             </a:r>
           </a:p>
@@ -428,7 +955,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
@@ -446,12 +973,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,7 +988,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
@@ -479,12 +1006,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,7 +1021,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
@@ -512,12 +1039,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,7 +1054,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
@@ -545,12 +1072,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,7 +1087,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
@@ -578,12 +1105,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,7 +1120,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
@@ -611,12 +1138,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,7 +1220,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -715,10 +1242,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -728,6 +1255,72 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1641,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1677,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1744,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,291 +1773,276 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net inflows/(outflows) from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>271945</v>
+        <v>1052008</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>344025</v>
+        <v>700615</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>98319</v>
+        <v>288288</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-9308</v>
+        <v>119485</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-8628</v>
+        <v>71736</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net inflows/(outflows) from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-8628</v>
+        <v>71736</v>
       </c>
       <c r="K6" t="n">
-        <v>-9308</v>
+        <v>119485</v>
       </c>
       <c r="L6" t="n">
-        <v>98319</v>
+        <v>288288</v>
       </c>
       <c r="M6" t="n">
-        <v>344025</v>
+        <v>700615</v>
       </c>
       <c r="N6" t="n">
-        <v>271945</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>1052008</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>14</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>40.7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>36.3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>28.1</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>20.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net outflows from investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-223714</v>
+        <v>80119</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-258670</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>-490</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>-268</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>-125</v>
-      </c>
+        <v>25046</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net outflows from investing activities</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>-125</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-268</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-490</v>
+          <t>Loans and advances to customers</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>-258670</v>
+        <v>25046</v>
       </c>
       <c r="N7" t="n">
-        <v>-223714</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>80119</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>22</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>40.7</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>36.3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>28.1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>23.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net inflows/(outflows) from financing activities</t>
+          <t>Due to customers</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>14845</v>
+        <v>941013</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>39669</v>
+        <v>609964</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>9698</v>
+        <v>234882</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>31107</v>
+        <v>73627</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-730</v>
+        <v>42307</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net inflows/(outflows) from financing activities</t>
+          <t>Due to customers</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-730</v>
+        <v>42307</v>
       </c>
       <c r="K8" t="n">
-        <v>31107</v>
+        <v>73627</v>
       </c>
       <c r="L8" t="n">
-        <v>9698</v>
+        <v>234882</v>
       </c>
       <c r="M8" t="n">
-        <v>39669</v>
+        <v>609964</v>
       </c>
       <c r="N8" t="n">
-        <v>14845</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>941013</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>22</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>40.7</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>36.3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>28.1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>23.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of financial year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>394036</v>
+        <v>95877</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>330938</v>
+        <v>77347</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>181658</v>
+        <v>39481</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>74856</v>
+        <v>35081</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>53534</v>
+        <v>16949</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of financial year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>53534</v>
+        <v>16949</v>
       </c>
       <c r="K9" t="n">
-        <v>74856</v>
+        <v>35081</v>
       </c>
       <c r="L9" t="n">
-        <v>181658</v>
+        <v>39481</v>
       </c>
       <c r="M9" t="n">
-        <v>330938</v>
+        <v>77347</v>
       </c>
       <c r="N9" t="n">
-        <v>394036</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>95877</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>19</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>47.3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>29</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>15.4</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>1240</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>728</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>912</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>531</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>416.4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>345.4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>257.5</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>190.9</v>
       </c>
     </row>
@@ -1475,201 +2077,771 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income/(expense)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>10911</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5340</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1701</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-450</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Net interest income/(expense)</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>-450</v>
+      </c>
+      <c r="S13" t="n">
+        <v>121</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1701</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5340</v>
+      </c>
+      <c r="V13" t="n">
+        <v>10911</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>21232</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11671</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>8119</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>6644</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>7049</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>7049</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6644</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8119</v>
+      </c>
+      <c r="U14" t="n">
+        <v>11671</v>
+      </c>
+      <c r="V14" t="n">
+        <v>21232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-19378</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-14131</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-13829</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-15632</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-10134</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>-10134</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-15632</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-13829</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-14131</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-19378</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3434</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-5710</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-11868</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3085</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>-3085</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-11868</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-5710</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3434</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>95877</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>77347</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>39481</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>35081</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>16949</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>16949</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>35081</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>39481</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>77347</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>95877</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Net inflows/(outflows) from operating activities</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>271945</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>344025</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>98319</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-9308</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-8628</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Net inflows/(outflows) from operating activities</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>-8628</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>-9308</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>98319</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>344025</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>271945</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Net outflows from investing activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-223714</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-258670</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-490</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-268</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Net outflows from investing activities</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-268</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-490</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-258670</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-223714</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net inflows/(outflows) from financing activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>14845</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>39669</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>9698</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>31107</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-730</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net inflows/(outflows) from financing activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-730</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>31107</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>9698</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>39669</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>14845</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of financial year</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>394036</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>330938</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>181658</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>74856</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>53534</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of financial year</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>53534</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>74856</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>181658</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>330938</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>394036</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>20.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>36.3%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>23.9%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>36.3%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>23.9%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>36.3%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>40.7%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>11.0%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>15.4%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>29.0%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>47.3%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>531%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>912%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>728%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>1240%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>190.9%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>257.5%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>345.4%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>416.4%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2023 cash figures use the originally-reported (pre-restatement) balances — see the Cash Flow Statement sheet's note. All capital/liquidity ratios fell sharply from FY2021-2022 to FY2025 as the bank scaled its balance sheet roughly 7x following the 2022 iFAST Corporation acquisition and rebrand from BFC Bank.</t>
         </is>
@@ -1677,7 +2849,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A38:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1685,6 +2857,664 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13030</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>392607</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>273772</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>107539</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>86029</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>58982</v>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000. FY2021 not publicly disclosed at category level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>338558</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>237670</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>80249</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>47985</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>405</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>534</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>535</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Of which credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>590</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>301</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>778</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>779</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (position, FX and commodities)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>36743</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>15850</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4524</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1184</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>16311</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>19746</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>21454</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>35546</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>392607</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>273718</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>107539</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>86029</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="11" ht="200" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources - iFAST Global Bank Limited's own Table UK OV1 (Overview of risk weighted exposure amounts):
+FY2025/FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.21 (Table 4: UK OV1) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023/FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.15 (Table 4: UK OV1) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: not publicly disclosed at category level — the FY2021 (BFC Bank Limited) Pillar 3 Disclosures document's Section 6.3 'Pillar 1 capital requirement' promises a category breakdown but the table itself is absent from the published document (confirmed by reading the full section) - only the aggregate Total RWA figure exists that year (see the Total RWAs sheet) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf
+Genuine, not-force-reconciled discrepancy: the FY2025 Pillar 3 document's own FY2024 comparative differs slightly between its two tables - this OV1 table's FY2024 Total is £273,718k, while the same document's Table 1 (UK KM1) FY2024 Total is £273,772k (used on the Total RWAs sheet for consistency with that sheet's other years); both are the Bank's own disclosed figures, reproduced as reported rather than reconciled.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1827,7 +3657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1996,7 +3826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2165,7 +3995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2288,6 +4118,1584 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>394036</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>330938</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>181658</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>74856</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>53534</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Trade and other receivables</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>23808</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>18868</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>20732</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13382</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>11037</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Debt instruments held at amortised cost</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>539329</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>316623</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>58172</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>29436</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Debt instruments at fair value through profit or loss</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>23924</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>80119</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>25046</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>9680</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>8483</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2501</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>777</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial assets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3056</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>659</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>951</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>426</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1052008</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>700615</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>288288</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>119485</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>71736</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Trade and other payables</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>9524</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>9713</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9465</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>5742</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>8811</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Due to customers</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>941013</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>609964</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>234882</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>73627</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>42307</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>5594</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>3590</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>4066</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>3233</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>378</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1646</v>
+      </c>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>956131</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>623268</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>248807</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>84404</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>54787</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>124700</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>124700</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>84700</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>74700</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>40200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Contingent Capital Note</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Share option reserve</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>856</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>436</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments (AT1 Perpetual Note)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>14676</v>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>-44355</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>-47789</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-45329</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-39619</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-27751</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>95877</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>77347</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>39481</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>35081</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>16949</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1052008</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>700615</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>288288</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>119485</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>71736</v>
+      </c>
+    </row>
+    <row r="32" ht="180" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are iFAST Global Bank Limited's own Statement of Financial Position / Statement of Comprehensive Income / Statement of Changes in Equity:
+FY2025: iFAST Global Bank Ltd. Annual Report 2025, p.34-35 - https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202025.pdf
+FY2024: iFAST Global Bank Ltd. Annual Report 2024, p.32-33 - https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202024.pdf
+FY2023: iFAST Global Bank Ltd. Annual Report 2023, p.34-35 - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2022: iFAST Global Bank Ltd. Annual Report 2023, p.34-35 (FY2022 comparative column, plus the Statement of changes in equity's own FY2022 roll-forward detail) - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2021: iFAST Global Bank Ltd. Annual Report 2021, p.30-31 - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202021.pdf
+iFAST Global Bank Limited (company no. 04797759, formerly BFC Bank Limited until 31 March 2022) - solo/entity basis throughout (the Bank has no subsidiaries). No standalone Annual Report exists for FY2022 (BFC Bank Limited rebranded mid-year); FY2022 figures are iFAST Global Bank Ltd. Annual Report 2023's own FY2022 comparative column, which that report itself labels 'Restated' for the income statement (income-statement presentation was reorganised, not a numeric restatement - the loss figure of £(11,868)k for FY2022 is unchanged across every report that shows it). Balance sheet line items genuinely change across vintages: 'Debt instruments at fair value through profit or loss' only appears as its own line in FY2023 (absorbed elsewhere once reclassified in FY2024); 'Loans and advances to customers' and 'Debt instruments held at amortised cost' first appear from FY2022/FY2024 respectively as the Bank's balance sheet grew roughly 7x following the 2022 iFAST Corporation acquisition; 'Deferred tax' and 'Other equity instruments' (an AT1 Perpetual Note) first appear in FY2025 only.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A32:F32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000. There was no other comprehensive income in any of the 5 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>37524</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>22104</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>6213</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-26613</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-16764</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-4512</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-459</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-463</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income/(expense)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10911</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>5340</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1701</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-450</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>9086</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>6787</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4862</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4916</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4832</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-1888</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-1305</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-1260</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-1369</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>7871</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>4899</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3557</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3656</v>
+      </c>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net trading profit on foreign exchange</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2693</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1803</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2706</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>2996</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>4479</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Fair value gain/(loss) on derivatives</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>-194</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-37</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-531</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Allowance for impairment loss</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-303</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-179</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-119</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-109</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>21232</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11671</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8119</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6644</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7049</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-397</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-313</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-312</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-349</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-363</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Amortisation</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-149</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-141</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-159</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-635</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-18854</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-14009</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-12780</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-14688</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-9637</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Net foreign exchange gain/(loss)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>332</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-725</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-166</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-19378</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-14131</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-13829</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-15632</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-10134</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) from continuing operations</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1854</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-5710</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-8718</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-3085</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Loss from discontinued operations, net of tax</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n">
+        <v>-3150</v>
+      </c>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) before tax for the year</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1854</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-5710</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-11868</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-3085</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Tax credit/(expense)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3434</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-5710</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-11868</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-3085</v>
+      </c>
+    </row>
+    <row r="28" ht="200" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are iFAST Global Bank Limited's own Statement of Financial Position / Statement of Comprehensive Income / Statement of Changes in Equity:
+FY2025: iFAST Global Bank Ltd. Annual Report 2025, p.34-35 - https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202025.pdf
+FY2024: iFAST Global Bank Ltd. Annual Report 2024, p.32-33 - https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202024.pdf
+FY2023: iFAST Global Bank Ltd. Annual Report 2023, p.34-35 - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2022: iFAST Global Bank Ltd. Annual Report 2023, p.34-35 (FY2022 comparative column, plus the Statement of changes in equity's own FY2022 roll-forward detail) - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2021: iFAST Global Bank Ltd. Annual Report 2021, p.30-31 - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202021.pdf
+iFAST Global Bank Limited (company no. 04797759, formerly BFC Bank Limited until 31 March 2022) - solo/entity basis throughout (the Bank has no subsidiaries). No standalone Annual Report exists for FY2022 (BFC Bank Limited rebranded mid-year); FY2022 figures are iFAST Global Bank Ltd. Annual Report 2023's own FY2022 comparative column, which that report itself labels 'Restated' for the income statement (income-statement presentation was reorganised, not a numeric restatement - the loss figure of £(11,868)k for FY2022 is unchanged across every report that shows it). Balance sheet line items genuinely change across vintages: 'Debt instruments at fair value through profit or loss' only appears as its own line in FY2023 (absorbed elsewhere once reclassified in FY2024); 'Loans and advances to customers' and 'Debt instruments held at amortised cost' first appear from FY2022/FY2024 respectively as the Bank's balance sheet grew roughly 7x following the 2022 iFAST Corporation acquisition; 'Deferred tax' and 'Other equity instruments' (an AT1 Perpetual Note) first appear in FY2025 only. FY2025/FY2024 are the only years with a disclosed Tax line (FY2024's is a genuine nil, not a gap) - FY2023/FY2022/FY2021 show 'Loss before tax and loss for the year' as a single figure with no separate tax charge disclosed. FY2022 is the only year to separately disclose discontinued operations (a £3,150k loss); every other year's activities are entirely continuing operations. 'Net fee and commission income' and 'Allowance for impairment loss' are not disclosed as their own subtotal/line in FY2021 - left blank rather than computed, since that year's own report doesn't present them that way.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A28:F28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000 — read chronologically, oldest to newest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Contingent Capital Note</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Share option reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>40200</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>-27751</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>16949</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n">
+        <v>-11868</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-11868</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Release of contingent capital note</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>-4500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Share capital issuance</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>34500</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>34500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>74700</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>-39619</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>35081</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>-5710</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-5710</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Share capital issuance</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>84700</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n">
+        <v>-45329</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>39481</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-2460</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Share capital issuance</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>326</v>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>124700</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>436</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-47789</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>77347</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>3434</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>3434</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>AT1 issuance</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n">
+        <v>15023</v>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>15023</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>AT1 note interest</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n">
+        <v>-347</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-347</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>124700</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>856</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>14676</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-44355</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>95877</v>
+      </c>
+    </row>
+    <row r="23" ht="210" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are iFAST Global Bank Limited's own Statement of Financial Position / Statement of Comprehensive Income / Statement of Changes in Equity:
+FY2025: iFAST Global Bank Ltd. Annual Report 2025, p.34-35 - https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202025.pdf
+FY2024: iFAST Global Bank Ltd. Annual Report 2024, p.32-33 - https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202024.pdf
+FY2023: iFAST Global Bank Ltd. Annual Report 2023, p.34-35 - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2022: iFAST Global Bank Ltd. Annual Report 2023, p.34-35 (FY2022 comparative column, plus the Statement of changes in equity's own FY2022 roll-forward detail) - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2021: iFAST Global Bank Ltd. Annual Report 2021, p.30-31 - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202021.pdf
+iFAST Global Bank Limited (company no. 04797759, formerly BFC Bank Limited until 31 March 2022) - solo/entity basis throughout (the Bank has no subsidiaries). No standalone Annual Report exists for FY2022 (BFC Bank Limited rebranded mid-year); FY2022 figures are iFAST Global Bank Ltd. Annual Report 2023's own FY2022 comparative column, which that report itself labels 'Restated' for the income statement (income-statement presentation was reorganised, not a numeric restatement - the loss figure of £(11,868)k for FY2022 is unchanged across every report that shows it). Balance sheet line items genuinely change across vintages: 'Debt instruments at fair value through profit or loss' only appears as its own line in FY2023 (absorbed elsewhere once reclassified in FY2024); 'Loans and advances to customers' and 'Debt instruments held at amortised cost' first appear from FY2022/FY2024 respectively as the Bank's balance sheet grew roughly 7x following the 2022 iFAST Corporation acquisition; 'Deferred tax' and 'Other equity instruments' (an AT1 Perpetual Note) first appear in FY2025 only. Equity reconciliation ladder: every year's closing balance ties exactly to both the next year's own reported opening balance and that year's own Balance Sheet Total equity - zero plug rows needed anywhere in this 5-year window, including through FY2022's 'Release of contingent capital note' (£4,500k, zeroing that reserve) - an easy-to-miss movement caught by reading the FY2023 Annual Report's own equity statement in full, which is also the only source disclosing FY2022's own detailed equity roll-forward (no standalone FY2022 Annual Report exists). One genuine, not-force-reconciled discrepancy: FY2022's 'Share capital issuance' is £34,500k per the Statement of Changes in Equity, but the pre-existing Cash Flow Statement's 'Proceeds from the issue of ordinary shares' for FY2022 is £30,000k - both are the Bank's own disclosed figures from the same Annual Report, reproduced as reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3055,7 +6463,266 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Asset Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000. Entire book has sat in Stage 1 throughout FY2021-FY2025 - a genuine feature, not a gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Aggregate credit-risk exposure by IFRS 9 stage (cash balances, receivables, debt instruments, loans and advances to customers, derivatives)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 gross exposure</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>896500</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>609339</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>261048</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>111457</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>53027</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 gross exposure</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 gross exposure</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total gross exposure</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>896500</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>609339</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>261048</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>111457</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>53027</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Less: allowance for impairment</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-752</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-449</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-270</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-151</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net exposure</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>895748</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>608890</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>260778</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>111306</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>52985</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ECL coverage ratio (allowance / gross exposure)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="190" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Sources - iFAST Global Bank Limited's own 'maximum exposure to credit risk by class of financial asset' table (aggregates cash balances with central banks/due from banks, trade receivables, debt instruments, loans and advances to customers, and derivative financial instruments; excludes Money Market Funds, which sit within cash and cash equivalents but outside this note):
+FY2025/FY2024: iFAST Global Bank Ltd. Annual Report 2025, p.58-59 (Note 27, Credit risk) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202025.pdf
+FY2023: iFAST Global Bank Ltd. Annual Report 2023, p.58-59 (Note 29, Credit risk) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2022: iFAST Global Bank Ltd. Annual Report 2023, p.59 (Note 29, Credit risk, FY2022 comparative column) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202023.pdf
+FY2021: iFAST Global Bank Ltd. Annual Report 2021, p.51 (Note 25, Credit risk) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Ltd.%20Annual%20Report%202021.pdf
+The Bank's loan book is entirely business-to-business/short-tenor in nature; no Stage 2 or Stage 3 balance has existed in any of the 5 years covered by this workbook (confirmed by reading each note in full). Note that 'Loans and advances to customers' only exists as a distinct exposure class from FY2024 onward (see the Balance Sheet sheet's entity note) - it is already included within the aggregate figures above for the years in which it exists.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3158,7 +6825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3271,7 +6938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3380,460 +7047,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>93994</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>76953</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>39032</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35017</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13030</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — Total RWAs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>392607</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>273772</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>107539</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>86029</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>58982</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -240,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -264,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -288,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -312,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -438,7 +438,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -462,7 +462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,7 +486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -510,7 +510,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -553,8 +553,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -593,13 +593,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -636,7 +636,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -679,8 +679,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -719,13 +719,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -762,7 +762,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -786,7 +786,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -810,7 +810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -834,7 +834,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -877,8 +877,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -917,13 +917,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -959,14 +959,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -992,14 +992,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1025,14 +1025,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1058,14 +1058,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1091,14 +1091,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1124,14 +1124,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1175,8 +1175,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1215,7 +1215,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1230,9 +1230,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1252,9 +1252,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1274,9 +1274,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1296,9 +1296,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1318,9 +1318,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2009,6 +2009,9 @@
           <t>LCR</t>
         </is>
       </c>
+      <c r="AP10" t="n">
+        <v>1109</v>
+      </c>
       <c r="AQ10" t="n">
         <v>1240</v>
       </c>
@@ -2804,7 +2807,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1109%</t>
         </is>
       </c>
     </row>
@@ -3738,10 +3741,8 @@
       <c r="E4" s="6" t="n">
         <v>65205</v>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
+      <c r="F4" s="6" t="n">
+        <v>26728</v>
       </c>
     </row>
     <row r="5">
@@ -3762,10 +3763,8 @@
       <c r="E5" s="6" t="n">
         <v>5258</v>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
+      <c r="F5" s="6" t="n">
+        <v>2411</v>
       </c>
     </row>
     <row r="6">
@@ -3796,14 +3795,14 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1109%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: The FY2021 (BFC Bank Limited) Pillar 3 Disclosures document has no LCR/liquidity section at all — only Leverage, Asset Encumbrance, Own funds, Capital Adequacy and Remuneration are covered — so FY2021 is genuinely not disclosed, not merely omitted from this workbook.</t>
+          <t>Note: FY2021's (BFC Bank Limited) Pillar 3 Disclosures disclose the liquidity table in the Market Risk section (p.18): liquidity buffer/HQLA £26,728k, total net cash outflows £2,411k and LCR 1,109%. These are the Bank's own figures; the report states that BFC Bank refers to the renamed iFAST Global Bank Limited.</t>
         </is>
       </c>
     </row>

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -240,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -264,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -288,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -312,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -438,7 +438,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -462,7 +462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,7 +486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -510,7 +510,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -553,8 +553,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -593,13 +593,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -636,7 +636,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -679,8 +679,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -719,13 +719,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -762,7 +762,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -786,7 +786,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -810,7 +810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -834,7 +834,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -877,8 +877,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -917,13 +917,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -959,14 +959,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -992,14 +992,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1025,14 +1025,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1058,14 +1058,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1091,14 +1091,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1124,14 +1124,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1175,8 +1175,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1215,7 +1215,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1230,9 +1230,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1252,9 +1252,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1274,9 +1274,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1296,9 +1296,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1318,9 +1318,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -3321,7 +3321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -3342,7 +3342,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, £'000. FY2021 not publicly disclosed at category level.</t>
+          <t>Solo basis, £'000. FY2025-FY2022 as directly disclosed (UK OV1); FY2021 derived from disclosed Pillar 1 capital requirement x 12.5 - see the two SECTION blocks below and the sources note.</t>
         </is>
       </c>
     </row>
@@ -3379,139 +3379,233 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Credit risk (excluding CCR)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>338558</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>237670</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>80249</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>47985</v>
-      </c>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>UK OV1 — Overview of risk weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Counterparty credit risk (CCR)</t>
+          <t>Credit risk (excluding CCR)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>405</v>
+        <v>338558</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>152</v>
+        <v>237670</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>534</v>
+        <v>80249</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>535</v>
+        <v>47985</v>
       </c>
       <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Of which credit valuation adjustment (CVA)</t>
+          <t>Counterparty credit risk (CCR)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>590</v>
+        <v>405</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>301</v>
+        <v>152</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>778</v>
+        <v>534</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>779</v>
+        <v>535</v>
       </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Market risk (position, FX and commodities)</t>
+          <t>Of which credit valuation adjustment (CVA)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>36743</v>
+        <v>590</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>15850</v>
+        <v>301</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4524</v>
+        <v>778</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1184</v>
+        <v>779</v>
       </c>
       <c r="F7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>Market risk (position, FX and commodities)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>36743</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>15850</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4524</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1184</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Operational risk</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>16311</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C9" s="6" t="n">
         <v>19746</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D9" s="6" t="n">
         <v>21454</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>35546</v>
       </c>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Total risk-weighted exposure amount</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>392607</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>273718</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D10" s="5" t="n">
         <v>107539</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>86029</v>
       </c>
-      <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="11" ht="200" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Pillar 1 capital requirement × 12.5 (derived from disclosed capital requirement)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk &amp; counterparty risk (derived)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>31162.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (derived)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>9950</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Credit valuation adjustment (CVA) (derived)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk (derived)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>17850</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount (derived)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n">
+        <v>58987.5</v>
+      </c>
+    </row>
+    <row r="18" ht="200" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Sources - iFAST Global Bank Limited's own Table UK OV1 (Overview of risk weighted exposure amounts):
 FY2025/FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.21 (Table 4: UK OV1) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
 FY2023/FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.15 (Table 4: UK OV1) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: not publicly disclosed at category level — the FY2021 (BFC Bank Limited) Pillar 3 Disclosures document's Section 6.3 'Pillar 1 capital requirement' promises a category breakdown but the table itself is absent from the published document (confirmed by reading the full section) - only the aggregate Total RWA figure exists that year (see the Total RWAs sheet) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf
+FY2021 (derived, not directly disclosed as RWA): the FY2021 (BFC Bank Limited) Pillar 3 Disclosures document's Section 6.3 'Pillar 1 capital requirement', p.27, does carry the promised table (a scanned/rasterised table, missed by a prior session's plain-text extraction, which is why it was previously marked absent here - confirmed present by visually rendering the page): 'Capital Resources Requirement - Pillar 1' broken into Credit Risk &amp; Counterparty Risk (£2,493k) / Operational Risk (£1,428k) / Market Risk (£796k) / CVA (£2k), totalling £4,719k. Each figure below is that table's own capital-requirement figure divided by 8% (multiplied by 12.5), the standard, exact Basel/CRR Article 92 identity. Reconciles to within £5.5k of the Total RWAs sheet's own FY2021 figure (58,982) - https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf
 Genuine, not-force-reconciled discrepancy: the FY2025 Pillar 3 document's own FY2024 comparative differs slightly between its two tables - this OV1 table's FY2024 Total is £273,718k, while the same document's Table 1 (UK KM1) FY2024 Total is £273,772k (used on the Total RWAs sheet for consistency with that sheet's other years); both are the Bank's own disclosed figures, reproduced as reported rather than reconciled.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2879,14 +2880,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Tier 1 Ratio</t>
+          <t>iFAST Global Bank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, % of RWA</t>
+          <t>Solo basis, £'000</t>
         </is>
       </c>
     </row>
@@ -2925,39 +2926,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13030</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
+          <t>Note: FY2021's Pillar 3 disclosure did not use the UK KM1 template; the Tier 1 capital figure is taken from the Leverage Ratio Common Disclosure table, and equals Total Own Funds as no Tier 2 capital was held.</t>
         </is>
       </c>
     </row>
@@ -3000,14 +2991,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Total Capital</t>
+          <t>iFAST Global Bank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, £'000</t>
+          <t>Solo basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3046,29 +3037,39 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>93994</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>76953</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>39032</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35017</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13030</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
+          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
         </is>
       </c>
     </row>
@@ -3111,14 +3112,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Total Capital Ratio</t>
+          <t>iFAST Global Bank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, % of RWA</t>
+          <t>Solo basis, £'000</t>
         </is>
       </c>
     </row>
@@ -3157,39 +3158,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13030</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
+          <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
         </is>
       </c>
     </row>
@@ -3213,6 +3204,127 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3315,7 +3427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3611,7 +3723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3749,171 +3861,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, £'000 / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA) (£'000)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>279890</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>301040</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>180356</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>65205</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>26728</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value (£'000)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>52750</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>33002</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>24764</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>5258</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity coverage ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>531%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>912%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>728%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>1240%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>1109%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's (BFC Bank Limited) Pillar 3 Disclosures disclose the liquidity table in the Market Risk section (p.18): liquidity buffer/HQLA £26,728k, total net cash outflows £2,411k and LCR 1,109%. These are the Bank's own figures; the report states that BFC Bank refers to the renamed iFAST Global Bank Limited.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3939,7 +3886,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — NSFR</t>
+          <t>iFAST Global Bank Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -3985,87 +3932,83 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding (£'000)</t>
+          <t>Total high-quality liquid assets (HQLA) (£'000)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>835880</v>
+        <v>279890</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>555781</v>
+        <v>301040</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>173025</v>
+        <v>180356</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>92023</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
+        <v>65205</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>26728</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding (£'000)</t>
+          <t>Total net cash outflows, adjusted value (£'000)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>437854</v>
+        <v>52750</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>215858</v>
+        <v>33002</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50090</v>
+        <v>24764</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>22101</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
+        <v>5258</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (%)</t>
+          <t>Liquidity coverage ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>190.9%</t>
+          <t>531%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>257.5%</t>
+          <t>912%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>345.4%</t>
+          <t>728%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>416.4%</t>
+          <t>1240%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1109%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 is genuinely not disclosed — see the LCR sheet's note; the FY2021 Pillar 3 document predates this bank's NSFR/LCR disclosure section entirely.</t>
+          <t>Note: FY2021's (BFC Bank Limited) Pillar 3 Disclosures disclose the liquidity table in the Market Risk section (p.18): liquidity buffer/HQLA £26,728k, total net cash outflows £2,411k and LCR 1,109%. These are the Bank's own figures; the report states that BFC Bank refers to the renamed iFAST Global Bank Limited.</t>
         </is>
       </c>
     </row>
@@ -4089,6 +4032,175 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>835880</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>555781</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>173025</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>92023</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>437854</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>215858</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>50090</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>22101</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>190.9%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>257.5%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>345.4%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>416.4%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 is genuinely not disclosed — see the LCR sheet's note; the FY2021 Pillar 3 document predates this bank's NSFR/LCR disclosure section entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6821,10 +6933,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -6835,21 +6947,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — CET1 Capital</t>
+          <t>iFAST Global Bank Limited — UK KM1 Key Metrics Template</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, £'000</t>
+          <t>Solo basis, as published. Amounts in £'000; ratios as printed.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6879,40 +6991,830 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1 Common Equity Tier 1 (CET1) capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>79319</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>76953</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>39032</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>35017</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>8530</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2 Tier 1 capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>13030</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3 Total capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>13030</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4 Total risk-weighted exposure amount (£'000)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>392607</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>273772</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>107539</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>86029</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>58982</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5 Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>14.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6 Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>22.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7 Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>22.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c Additional T2 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8 Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>9 Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>11 Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>15.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>12 CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>13 Total exposure measure excluding claims on central banks (£'000)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>868024</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>501384</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>136351</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>74160</v>
+      </c>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>14 Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>29.0%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>47.3%</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>15 Total high-quality liquid assets (HQLA) (£'000)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>279890</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>301040</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>180356</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>65205</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>19333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a Cash outflows - Total weighted value (£'000)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>210999</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>132007</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>92748</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>21034</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>9729</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b Cash inflows - Total weighted value (£'000)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>158249</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>99006</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>67984</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>15775</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>7297</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>16 Total net cash outflows (adjusted value) (£'000)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>52750</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>33002</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>24764</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>5258</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>17 Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>531%</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>912%</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>728%</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>1240%</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>795%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>18 Total available stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>835880</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>555781</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>173025</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>92023</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>19 Total required stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>437854</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>215858</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>50090</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>22101</v>
+      </c>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>20 NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>190.9%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>257.5%</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>345.4%</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>416.4%</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="39" ht="330" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited's own 'Table 1: UK KM1- Key Metrics template', reproduced as published. Solo basis (the Bank trades as a single entity, has no subsidiaries or associates and is not part of a UK consolidation sub-group, so its Pillar 3 disclosures are prepared on an individual basis). Amounts in £'000, the presentation currency of the template itself.
+FY2025: Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1, section 4 'Key Metrics'), its OWN reporting year — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2024: Pillar 3 Disclosures 2024, p.11 (Table 1: UK KM1), its OWN reporting year — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202024.pdf
+FY2023: Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1), its OWN reporting year — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2022: Pillar 3 Disclosures 2022, p.13 (Table 1: UK KM1), its OWN reporting year — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202022.pdf
+FY2021: NOT from a FY2021 KM1 — the Pillar 3 Disclosures 2021 document prints no KM1 template at all (see the sheet note). The FY2021 column here is the 2022 edition's own '31-Dec-21' COMPARATIVE column, p.13 — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202022.pdf
+Each of FY2025/FY2024/FY2023/FY2022 is taken from the edition in which that year is the REPORTING year, not from a later edition's comparative.
+THE 2025 EDITION PRINTS THE TEMPLATE TWICE, WITH DIFFERENT FIGURES AND NO CAPTION ON THE SECOND COPY. This sheet reproduces the FIRST copy — the one the document captions 'Table 1: UK KM1- Key Metrics template' on p.16, under the section heading '4. Key Metrics'. A second, visually identical table follows immediately on p.17 carrying the same two column headers (31-Dec-25 and 31-Dec-24) and the same £'000 unit, but no table number, no caption, no heading and no footnote explaining it. Seven of its figures differ from the first copy's: CET1 capital 77,465 (vs 79,319), Tier 1 and Total capital 92,141 (vs 93,994), total RWAs 391,949 (vs 392,607), CET1 ratio 19.8% (vs 20.2%), Tier 1 and Total capital ratio 23.5% (vs 23.9%), leverage exposure measure 867,366 (vs 868,024) and leverage ratio 10.7% (vs 11.0%), available stable funding 832,447 (vs 835,880), required stable funding 436,274 (vs 437,854) and NSFR 190.8% (vs 190.9%). Its 31-Dec-24 comparative column is identical to the first copy's throughout. This is recorded as a source defect and is NOT reconciled. The first copy is the one corroborated twice over inside the same document: its Table 2 (UK CC1, Composition of regulatory own funds, p.20) builds CET1 up component by component to exactly 79,319, then AT1 14,676, Tier 1 and Total capital 93,994, total risk exposure amount 392,607 and ratios 20.20% / 23.94% / 23.94%; and its Table 4 (UK OV1, p.21) sums its risk categories to the same 392,607. Nothing in the document corroborates the second copy's figures, and it is not referenced anywhere in the text or contents page.
+FY2021 IS FILLED FROM A COMPARATIVE. The FY2021 edition (published under the Bank's former name, BFC Bank Limited) prints no KM1 template: its section 1.1 'Key Metrics' is four highlight boxes giving CET1 £8.8m, a CET1 ratio of 14%, an LCR of 1109% and a leverage ratio of 19% — four figures, no row numbers, no SREP rows, no buffer rows, no NSFR rows. On the row-set test that is not the template, so there is no own-edition table for FY2021 to displace, and the column here is the 2022 edition's own 31-Dec-21 comparative. That comparative leaves rows 13, 14 and 18-20 empty, so those cells are blank here; row 9 is printed as an explicit '0.0%' and is recorded as a zero.
+PRECISION IS THE BANK'S OWN AND CHANGES BETWEEN EDITIONS. The 2022 edition prints its 31-Dec-21 comparative ratios to two decimals (14.46%, 22.09%) and its own 31-Dec-22 ratios to one (40.7%). Both are reproduced as printed rather than standardised. Row UK 7d likewise mixes precisions across editions (12.9% in 2022/2023, 11.45% in 2024/2025) and is left as published.
+THE TWO SOURCES FOR FY2021 LIQUIDITY DISAGREE, AND BOTH ARE THE BANK'S OWN. This sheet's FY2021 LCR is 795%, taken from the 2022 edition's 31-Dec-21 comparative along with the rest of that column. The LCR sheet in this workbook shows 1109% for the same date, taken from the FY2021 edition's own liquidity table (p.18), which also prints HQLA of £26,728k and net cash outflows of £2,411k against the 2022 edition's £19,333k and £2,432k for the same date. The difference is in the HQLA numerator, not the outflows, and the bank offers no reconciliation or restatement note anywhere in the 2022 edition. This is a genuine cross-edition divergence and is recorded on both sheets rather than reconciled: the KM1 sheet shows what the 2022 edition's KM1 template printed for 31-Dec-21, and the LCR sheet shows what the FY2021 edition's own liquidity table printed for the same date. Reading row 17 of this sheet beside the LCR sheet will therefore show two different FY2021 figures, and that is the two editions disagreeing, not a transcription error in either. Which of the two the bank would now stand behind is not something these documents settle, so neither figure is presented as superseding the other.
+Rows UK 8a, UK 9a, 10, UK 10a and UK 14a-14f are absent from every edition of this bank's template — it prints rows 1-7, UK 7a-7d, 8, 9, 11, UK 11a, 12, 13, 14, 15, UK 16a, UK 16b, 16, 17 and 18-20 only. A row the bank did not print is left out rather than shown as zero.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6938,14 +7840,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — CET1 Ratio</t>
+          <t>iFAST Global Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, % of RWA</t>
+          <t>Solo basis, £'000</t>
         </is>
       </c>
     </row>
@@ -6984,33 +7886,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>79319</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>8530</v>
       </c>
     </row>
     <row r="6" ht="100" customHeight="1">
@@ -7037,7 +7929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7051,14 +7943,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Tier 1 Capital</t>
+          <t>iFAST Global Bank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, £'000</t>
+          <t>Solo basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -7097,34 +7989,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>93994</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>76953</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>39032</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35017</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13030</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's Pillar 3 disclosure did not use the UK KM1 template; the Tier 1 capital figure is taken from the Leverage Ratio Common Disclosure table, and equals Total Own Funds as no Tier 2 capital was held.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Common Equity Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
 FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
@@ -7134,9 +8029,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -7804,6 +7804,7 @@
 FY2022: Pillar 3 Disclosures 2022, p.13 (Table 1: UK KM1), its OWN reporting year — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202022.pdf
 FY2021: NOT from a FY2021 KM1 — the Pillar 3 Disclosures 2021 document prints no KM1 template at all (see the sheet note). The FY2021 column here is the 2022 edition's own '31-Dec-21' COMPARATIVE column, p.13 — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202022.pdf
 Each of FY2025/FY2024/FY2023/FY2022 is taken from the edition in which that year is the REPORTING year, not from a later edition's comparative.
+ROWS 1, 2 AND 3 ARE EQUAL IN THE SOURCE FOR FY2024, FY2023 AND FY2022 - READ FROM THE DOCUMENTS ON 2026-09-18 AND RECORDED HERE SO THE QUESTION IS NOT RE-OPENED. The Pillar 3 Disclosures 2024 prints 76,953 on rows 1, 2 and 3 for FY2024 and 39,032 for FY2023; the Pillar 3 Disclosures 2023 prints 39,032 and 35,017 the same way. No Additional Tier 1 or Tier 2 line is populated in either edition's own-funds composition, which is why the three measures coincide. FY2025 is DISTINCT in the source - CET1 79,319 against Tier 1 and Total capital of 93,994 - and is held that way here, so the rows are told apart in this series wherever the Bank prints them apart.
 THE 2025 EDITION PRINTS THE TEMPLATE TWICE, WITH DIFFERENT FIGURES AND NO CAPTION ON THE SECOND COPY. This sheet reproduces the FIRST copy — the one the document captions 'Table 1: UK KM1- Key Metrics template' on p.16, under the section heading '4. Key Metrics'. A second, visually identical table follows immediately on p.17 carrying the same two column headers (31-Dec-25 and 31-Dec-24) and the same £'000 unit, but no table number, no caption, no heading and no footnote explaining it. Seven of its figures differ from the first copy's: CET1 capital 77,465 (vs 79,319), Tier 1 and Total capital 92,141 (vs 93,994), total RWAs 391,949 (vs 392,607), CET1 ratio 19.8% (vs 20.2%), Tier 1 and Total capital ratio 23.5% (vs 23.9%), leverage exposure measure 867,366 (vs 868,024) and leverage ratio 10.7% (vs 11.0%), available stable funding 832,447 (vs 835,880), required stable funding 436,274 (vs 437,854) and NSFR 190.8% (vs 190.9%). Its 31-Dec-24 comparative column is identical to the first copy's throughout. This is recorded as a source defect and is NOT reconciled. The first copy is the one corroborated twice over inside the same document: its Table 2 (UK CC1, Composition of regulatory own funds, p.20) builds CET1 up component by component to exactly 79,319, then AT1 14,676, Tier 1 and Total capital 93,994, total risk exposure amount 392,607 and ratios 20.20% / 23.94% / 23.94%; and its Table 4 (UK OV1, p.21) sums its risk categories to the same 392,607. Nothing in the document corroborates the second copy's figures, and it is not referenced anywhere in the text or contents page.
 FY2021 IS FILLED FROM A COMPARATIVE. The FY2021 edition (published under the Bank's former name, BFC Bank Limited) prints no KM1 template: its section 1.1 'Key Metrics' is four highlight boxes giving CET1 £8.8m, a CET1 ratio of 14%, an LCR of 1109% and a leverage ratio of 19% — four figures, no row numbers, no SREP rows, no buffer rows, no NSFR rows. On the row-set test that is not the template, so there is no own-edition table for FY2021 to displace, and the column here is the 2022 edition's own 31-Dec-21 comparative. That comparative leaves rows 13, 14 and 18-20 empty, so those cells are blank here; row 9 is printed as an explicit '0.0%' and is recorded as a zero.
 PRECISION IS THE BANK'S OWN AND CHANGES BETWEEN EDITIONS. The 2022 edition prints its 31-Dec-21 comparative ratios to two decimals (14.46%, 22.09%) and its own 31-Dec-22 ratios to one (40.7%). Both are reproduced as printed rather than standardised. Row UK 7d likewise mixes precisions across editions (12.9% in 2022/2023, 11.45% in 2024/2025) and is left as published.

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -1682,6 +1682,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2840,7 +2841,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4115,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4139,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4171,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
         </is>
       </c>
     </row>
@@ -4267,27 +4268,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
         </is>
       </c>
     </row>

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="39" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2023 cash figures use the originally-reported (pre-restatement) balances — see the Cash Flow Statement sheet's note. All capital/liquidity ratios fell sharply from FY2021-2022 to FY2025 as the bank scaled its balance sheet roughly 7x following the 2022 iFAST Corporation acquisition and rebrand from BFC Bank.</t>
@@ -2946,7 +2946,7 @@
         <v>13030</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021's Pillar 3 disclosure did not use the UK KM1 template; the Tier 1 capital figure is taken from the Leverage Ratio Common Disclosure table, and equals Total Own Funds as no Tier 2 capital was held.</t>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
@@ -3178,7 +3178,7 @@
         <v>13030</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
@@ -3841,10 +3841,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="182" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 exposure measure is the 'Leverage ratio total exposure measure' and ratio is the 'Regulatory Leverage Ratio' from the Leverage Ratio Common Disclosure table (pre-KM1-template disclosure format).</t>
+          <t xml:space="preserve">Note: FY2021 exposure measure is the 'Leverage ratio total exposure measure' and ratio is the 'Regulatory Leverage Ratio' from the Leverage Ratio Common Disclosure table (pre-KM1-template disclosure format).
+ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
+HOW THAT WAS ESTABLISHED: all 5 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (5 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. Every match was opened and read on 2026-10-09; none is an in-scope disclosure. The remaining matches are NOT leverage at all: template UK CC1 (composition of regulatory own funds) has its own rows UK-25a 'Losses for the current financial year' and UK-25b 'Foreseeable tax charges', which collide with the leverage template's UK-25a/UK-25c row numbering. A row number alone never identifies a template. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
+THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
         </is>
       </c>
     </row>
@@ -4006,7 +4009,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021's (BFC Bank Limited) Pillar 3 Disclosures disclose the liquidity table in the Market Risk section (p.18): liquidity buffer/HQLA £26,728k, total net cash outflows £2,411k and LCR 1,109%. These are the Bank's own figures; the report states that BFC Bank refers to the renamed iFAST Global Bank Limited.</t>
@@ -4175,7 +4178,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 is genuinely not disclosed — see the LCR sheet's note; the FY2021 Pillar 3 document predates this bank's NSFR/LCR disclosure section entirely.</t>
@@ -4292,7 +4295,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: MREL is not disclosed in any of the 5 years' Pillar 3 documents — iFAST Global Bank Limited (formerly BFC Bank Limited) is a small bank below the threshold at which the Bank of England sets an MREL requirement above minimum capital requirements.</t>
@@ -5449,7 +5452,7 @@
         <v>-3085</v>
       </c>
     </row>
-    <row r="28" ht="200" customHeight="1">
+    <row r="28" ht="208" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are iFAST Global Bank Limited's own Statement of Financial Position / Statement of Comprehensive Income / Statement of Changes in Equity:
@@ -5875,7 +5878,7 @@
         <v>95877</v>
       </c>
     </row>
-    <row r="23" ht="210" customHeight="1">
+    <row r="23" ht="234" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are iFAST Global Bank Limited's own Statement of Financial Position / Statement of Comprehensive Income / Statement of Changes in Equity:
@@ -6649,7 +6652,7 @@
         <v>53534</v>
       </c>
     </row>
-    <row r="43" ht="130" customHeight="1">
+    <row r="43" ht="195" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Sources — iFAST Global Bank Limited (company no. 04797759, formerly BFC Bank Limited until 31 March 2022) standalone Statement of cash flows, £'000:
@@ -6934,7 +6937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -7795,7 +7798,7 @@
       </c>
       <c r="F37" s="6" t="n"/>
     </row>
-    <row r="39" ht="330" customHeight="1">
+    <row r="39" ht="377" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Sources — iFAST Global Bank Limited's own 'Table 1: UK KM1- Key Metrics template', reproduced as published. Solo basis (the Bank trades as a single entity, has no subsidiaries or associates and is not part of a UK consolidation sub-group, so its Pillar 3 disclosures are prepared on an individual basis). Amounts in £'000, the presentation currency of the template itself.
@@ -7808,14 +7811,22 @@
 ROWS 1, 2 AND 3 ARE EQUAL IN THE SOURCE FOR FY2024, FY2023 AND FY2022 - READ FROM THE DOCUMENTS ON 2026-09-18 AND RECORDED HERE SO THE QUESTION IS NOT RE-OPENED. The Pillar 3 Disclosures 2024 prints 76,953 on rows 1, 2 and 3 for FY2024 and 39,032 for FY2023; the Pillar 3 Disclosures 2023 prints 39,032 and 35,017 the same way. No Additional Tier 1 or Tier 2 line is populated in either edition's own-funds composition, which is why the three measures coincide. FY2025 is DISTINCT in the source - CET1 79,319 against Tier 1 and Total capital of 93,994 - and is held that way here, so the rows are told apart in this series wherever the Bank prints them apart.
 THE 2025 EDITION PRINTS THE TEMPLATE TWICE, WITH DIFFERENT FIGURES AND NO CAPTION ON THE SECOND COPY. This sheet reproduces the FIRST copy — the one the document captions 'Table 1: UK KM1- Key Metrics template' on p.16, under the section heading '4. Key Metrics'. A second, visually identical table follows immediately on p.17 carrying the same two column headers (31-Dec-25 and 31-Dec-24) and the same £'000 unit, but no table number, no caption, no heading and no footnote explaining it. Seven of its figures differ from the first copy's: CET1 capital 77,465 (vs 79,319), Tier 1 and Total capital 92,141 (vs 93,994), total RWAs 391,949 (vs 392,607), CET1 ratio 19.8% (vs 20.2%), Tier 1 and Total capital ratio 23.5% (vs 23.9%), leverage exposure measure 867,366 (vs 868,024) and leverage ratio 10.7% (vs 11.0%), available stable funding 832,447 (vs 835,880), required stable funding 436,274 (vs 437,854) and NSFR 190.8% (vs 190.9%). Its 31-Dec-24 comparative column is identical to the first copy's throughout. This is recorded as a source defect and is NOT reconciled. The first copy is the one corroborated twice over inside the same document: its Table 2 (UK CC1, Composition of regulatory own funds, p.20) builds CET1 up component by component to exactly 79,319, then AT1 14,676, Tier 1 and Total capital 93,994, total risk exposure amount 392,607 and ratios 20.20% / 23.94% / 23.94%; and its Table 4 (UK OV1, p.21) sums its risk categories to the same 392,607. Nothing in the document corroborates the second copy's figures, and it is not referenced anywhere in the text or contents page.
 FY2021 IS FILLED FROM A COMPARATIVE. The FY2021 edition (published under the Bank's former name, BFC Bank Limited) prints no KM1 template: its section 1.1 'Key Metrics' is four highlight boxes giving CET1 £8.8m, a CET1 ratio of 14%, an LCR of 1109% and a leverage ratio of 19% — four figures, no row numbers, no SREP rows, no buffer rows, no NSFR rows. On the row-set test that is not the template, so there is no own-edition table for FY2021 to displace, and the column here is the 2022 edition's own 31-Dec-21 comparative. That comparative leaves rows 13, 14 and 18-20 empty, so those cells are blank here; row 9 is printed as an explicit '0.0%' and is recorded as a zero.
-PRECISION IS THE BANK'S OWN AND CHANGES BETWEEN EDITIONS. The 2022 edition prints its 31-Dec-21 comparative ratios to two decimals (14.46%, 22.09%) and its own 31-Dec-22 ratios to one (40.7%). Both are reproduced as printed rather than standardised. Row UK 7d likewise mixes precisions across editions (12.9% in 2022/2023, 11.45% in 2024/2025) and is left as published.
+PRECISION IS THE BANK'S OWN AND CHANGES BETWEEN EDITIONS. The 2022 edition prints its 31-Dec-21 comparative ratios to two decimals (14.46%, 22.09%) and its own 31-Dec-22 ratios to one (40.7%). Both are reproduced as printed rather than standardised. Row UK 7d likewise mixes precisions across editions (12.9% in 2022/2023, 11.45% in 2024/2025) and is left as published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="330" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 THE TWO SOURCES FOR FY2021 LIQUIDITY DISAGREE, AND BOTH ARE THE BANK'S OWN. This sheet's FY2021 LCR is 795%, taken from the 2022 edition's 31-Dec-21 comparative along with the rest of that column. The LCR sheet in this workbook shows 1109% for the same date, taken from the FY2021 edition's own liquidity table (p.18), which also prints HQLA of £26,728k and net cash outflows of £2,411k against the 2022 edition's £19,333k and £2,432k for the same date. The difference is in the HQLA numerator, not the outflows, and the bank offers no reconciliation or restatement note anywhere in the 2022 edition. This is a genuine cross-edition divergence and is recorded on both sheets rather than reconciled: the KM1 sheet shows what the 2022 edition's KM1 template printed for 31-Dec-21, and the LCR sheet shows what the FY2021 edition's own liquidity table printed for the same date. Reading row 17 of this sheet beside the LCR sheet will therefore show two different FY2021 figures, and that is the two editions disagreeing, not a transcription error in either. Which of the two the bank would now stand behind is not something these documents settle, so neither figure is presented as superseding the other.
 Rows UK 8a, UK 9a, 10, UK 10a and UK 14a-14f are absent from every edition of this bank's template — it prints rows 1-7, UK 7a-7d, 8, 9, 11, UK 11a, 12, 13, 14, 15, UK 16a, UK 16b, 16, 17 and 18-20 only. A row the bank did not print is left out rather than shown as zero.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
+++ b/banks/IFAST GLOBAL BANK LIMITED FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2867,7 +2868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2881,14 +2882,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Tier 1 Capital</t>
+          <t>iFAST Global Bank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, £'000</t>
+          <t>Solo basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -2927,34 +2928,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>93994</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>76953</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>39032</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35017</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13030</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's Pillar 3 disclosure did not use the UK KM1 template; the Tier 1 capital figure is taken from the Leverage Ratio Common Disclosure table, and equals Total Own Funds as no Tier 2 capital was held.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Common Equity Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
 FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
@@ -2964,9 +2968,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2992,14 +2995,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Tier 1 Ratio</t>
+          <t>iFAST Global Bank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, % of RWA</t>
+          <t>Solo basis, £'000</t>
         </is>
       </c>
     </row>
@@ -3038,39 +3041,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13030</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
+          <t>Note: FY2021's Pillar 3 disclosure did not use the UK KM1 template; the Tier 1 capital figure is taken from the Leverage Ratio Common Disclosure table, and equals Total Own Funds as no Tier 2 capital was held.</t>
         </is>
       </c>
     </row>
@@ -3113,14 +3106,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Total Capital</t>
+          <t>iFAST Global Bank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, £'000</t>
+          <t>Solo basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3159,29 +3152,39 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>93994</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>76953</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>39032</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35017</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>13030</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
+          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table, which equals the Tier 1 ratio as no Tier 2 capital was held that year.</t>
         </is>
       </c>
     </row>
@@ -3224,14 +3227,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — Total Capital Ratio</t>
+          <t>iFAST Global Bank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, % of RWA</t>
+          <t>Solo basis, £'000</t>
         </is>
       </c>
     </row>
@@ -3270,39 +3273,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>23.9%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>13030</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
+          <t>Note: FY2021 figure is 'Total Own funds' from the Own funds table (no Tier 2 capital held that year, so Total capital = Tier 1 capital).</t>
         </is>
       </c>
     </row>
@@ -3326,6 +3319,127 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is the 'Capital Adequacy Ratio' from the Own funds table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3428,7 +3542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3724,7 +3838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3865,171 +3979,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, £'000 / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA) (£'000)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>279890</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>301040</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>180356</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>65205</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>26728</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value (£'000)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>52750</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>33002</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>24764</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>5258</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity coverage ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>531%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>912%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>728%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>1240%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>1109%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's (BFC Bank Limited) Pillar 3 Disclosures disclose the liquidity table in the Market Risk section (p.18): liquidity buffer/HQLA £26,728k, total net cash outflows £2,411k and LCR 1,109%. These are the Bank's own figures; the report states that BFC Bank refers to the renamed iFAST Global Bank Limited.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4055,7 +4004,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — NSFR</t>
+          <t>iFAST Global Bank Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -4101,87 +4050,83 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding (£'000)</t>
+          <t>Total high-quality liquid assets (HQLA) (£'000)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>835880</v>
+        <v>279890</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>555781</v>
+        <v>301040</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>173025</v>
+        <v>180356</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>92023</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
-        </is>
+        <v>65205</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>26728</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding (£'000)</t>
+          <t>Total net cash outflows, adjusted value (£'000)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>437854</v>
+        <v>52750</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>215858</v>
+        <v>33002</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50090</v>
+        <v>24764</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>22101</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
-        </is>
+        <v>5258</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (%)</t>
+          <t>Liquidity coverage ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>190.9%</t>
+          <t>531%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>257.5%</t>
+          <t>912%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>345.4%</t>
+          <t>728%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>416.4%</t>
+          <t>1240%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
+          <t>1109%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 is genuinely not disclosed — see the LCR sheet's note; the FY2021 Pillar 3 document predates this bank's NSFR/LCR disclosure section entirely.</t>
+          <t>Note: FY2021's (BFC Bank Limited) Pillar 3 Disclosures disclose the liquidity table in the Market Risk section (p.18): liquidity buffer/HQLA £26,728k, total net cash outflows £2,411k and LCR 1,109%. These are the Bank's own figures; the report states that BFC Bank refers to the renamed iFAST Global Bank Limited.</t>
         </is>
       </c>
     </row>
@@ -4210,10 +4155,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -4224,12 +4169,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — MREL Ratio</t>
+          <t>iFAST Global Bank Limited — NSFR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo basis, £'000 / %</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4266,44 +4215,92 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
-        </is>
+          <t>Total available stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>835880</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>555781</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>173025</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>92023</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: MREL is not disclosed in any of the 5 years' Pillar 3 documents — iFAST Global Bank Limited (formerly BFC Bank Limited) is a small bank below the threshold at which the Bank of England sets an MREL requirement above minimum capital requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>437854</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>215858</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>50090</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>22101</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>190.9%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>257.5%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>345.4%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>416.4%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – UK NSFR in force only from 1 Jan 2022 (PRA PS17/21); FY2021 Pillar 3 prints no NSFR and the FY2022 KM1's 31-Dec-21 column leaves rows 18-20 empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 is genuinely not disclosed — see the LCR sheet's note; the FY2021 Pillar 3 document predates this bank's NSFR/LCR disclosure section entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
 FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
@@ -4314,8 +4311,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4916,6 +4913,123 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A32:F32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or statement in this year's Pillar 3, nor in the Annual Reports held (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: MREL is not disclosed in any of the 5 years' Pillar 3 documents — iFAST Global Bank Limited (formerly BFC Bank Limited) is a small bank below the threshold at which the Bank of England sets an MREL requirement above minimum capital requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
+FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
+FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
+FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6937,6 +7051,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>3.96%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>-4.21%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>-15.32%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>-45.62%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>-3.18%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>-14.46%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>-33.83%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>-18.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>-2.80%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-12.41%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>-1.98%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-9.93%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-4.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>iFAST Global Bank Limited's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="169" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. The bank's 70-page own-entity FY2025 annual report publishes profit, balance-sheet growth, capital, leverage, LCR, NSFR and detailed financial statements but no actual ROE, ROA or RoTE measure. Whole-document searches found only an unrelated director biography saying a former bank performed well in terms of ROE and a fund-investment return; neither is an iFAST Global Bank metric. The strategic financial-performance and capital/liquidity pages were visually checked. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2022, where return on equity is -45.62% on an average basis and -33.83% on a year-end basis.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit/(loss) for the year” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from iFAST Global Bank Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that iFAST Global Bank Limited publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘IFAST GLOBAL BANK LIMITED’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7828,109 +8183,6 @@
   <mergeCells count="2">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A39:F39"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>iFAST Global Bank Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>79319</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>76953</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>39032</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35017</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>8530</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — iFAST Global Bank Limited (formerly BFC Bank Limited) solo basis:
-FY2025 &amp; FY2024: iFAST Global Bank Limited Pillar 3 Disclosures 2025, p.16 (Table 1: UK KM1 - Key Metrics template) — https://static.ifastgb.com/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202025.pdf
-FY2023 &amp; FY2022: iFAST Global Bank Limited Pillar 3 Disclosures 2023, p.12 (Table 1: UK KM1- Key Metrics template) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202023.pdf
-FY2021: BFC Bank Limited Pillar 3 Disclosures 2021, p.25 / 23 (Own funds table / Leverage Ratio Common Disclosure table) — https://www.ifastgb.com/assets/static-file/investor-relations/iFAST%20Global%20Bank%20Limited%20Pillar%203%20Disclosures%202021.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7956,14 +8208,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited — CET1 Ratio</t>
+          <t>iFAST Global Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo basis, % of RWA</t>
+          <t>Solo basis, £'000</t>
         </is>
       </c>
     </row>
@@ -8002,33 +8254,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>28.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>40.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>79319</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>76953</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>39032</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>35017</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>8530</v>
       </c>
     </row>
     <row r="6" ht="100" customHeight="1">
